--- a/data/raw/김포 25년/항공통계상세조회(노선) (12).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (12).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="67">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>11818</t>
-  </si>
-  <si>
-    <t>2109643</t>
-  </si>
-  <si>
-    <t>17450</t>
+    <t>5913</t>
+  </si>
+  <si>
+    <t>1066823</t>
+  </si>
+  <si>
+    <t>8498</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,169 +53,166 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>552</t>
-  </si>
-  <si>
-    <t>100125</t>
-  </si>
-  <si>
-    <t>1004</t>
+    <t>276</t>
+  </si>
+  <si>
+    <t>49451</t>
+  </si>
+  <si>
+    <t>481</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
-    <t>125</t>
-  </si>
-  <si>
-    <t>15407</t>
-  </si>
-  <si>
-    <t>42</t>
+    <t>62</t>
+  </si>
+  <si>
+    <t>7486</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>김해(PUS)</t>
   </si>
   <si>
-    <t>1381</t>
-  </si>
-  <si>
-    <t>213152</t>
-  </si>
-  <si>
-    <t>813</t>
+    <t>690</t>
+  </si>
+  <si>
+    <t>107351</t>
+  </si>
+  <si>
+    <t>404</t>
   </si>
   <si>
     <t>나고야(NGO)</t>
   </si>
   <si>
+    <t>10228</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>5928</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>82908</t>
+  </si>
+  <si>
+    <t>1988</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>14178</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>7223</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>11007</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>11495</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>11598</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3810</t>
+  </si>
+  <si>
+    <t>712124</t>
+  </si>
+  <si>
+    <t>4506</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>9197</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>2134</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>124</t>
   </si>
   <si>
-    <t>20680</t>
-  </si>
-  <si>
-    <t>195</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>11401</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>744</t>
-  </si>
-  <si>
-    <t>167248</t>
-  </si>
-  <si>
-    <t>3074</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>27300</t>
-  </si>
-  <si>
-    <t>330</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>14771</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>21850</t>
-  </si>
-  <si>
-    <t>298</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>23372</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>23766</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>7611</t>
-  </si>
-  <si>
-    <t>1399783</t>
-  </si>
-  <si>
-    <t>10302</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>18301</t>
-  </si>
-  <si>
-    <t>219</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>3961</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>48526</t>
-  </si>
-  <si>
-    <t>811</t>
+    <t>24515</t>
+  </si>
+  <si>
+    <t>315</t>
   </si>
 </sst>
 </file>
@@ -380,13 +377,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="E6" t="s" s="0">
+      <c r="F6" t="s" s="0">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -397,16 +394,16 @@
         <v>11</v>
       </c>
       <c r="C7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="D7" t="s" s="0">
+      <c r="E7" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="E7" t="s" s="0">
+      <c r="F7" t="s" s="0">
         <v>30</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -417,16 +414,16 @@
         <v>11</v>
       </c>
       <c r="C8" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="D8" t="s" s="0">
+      <c r="E8" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="E8" t="s" s="0">
+      <c r="F8" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="F8" t="s" s="0">
-        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -437,16 +434,16 @@
         <v>11</v>
       </c>
       <c r="C9" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="D9" t="s" s="0">
+      <c r="E9" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="E9" t="s" s="0">
+      <c r="F9" t="s" s="0">
         <v>38</v>
-      </c>
-      <c r="F9" t="s" s="0">
-        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -457,16 +454,16 @@
         <v>11</v>
       </c>
       <c r="C10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="D10" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s" s="0">
+      <c r="F10" t="s" s="0">
         <v>41</v>
-      </c>
-      <c r="F10" t="s" s="0">
-        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -477,16 +474,16 @@
         <v>11</v>
       </c>
       <c r="C11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="D11" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s" s="0">
+      <c r="F11" t="s" s="0">
         <v>44</v>
-      </c>
-      <c r="F11" t="s" s="0">
-        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -497,16 +494,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="D12" t="s" s="0">
+      <c r="E12" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="E12" t="s" s="0">
+      <c r="F12" t="s" s="0">
         <v>48</v>
-      </c>
-      <c r="F12" t="s" s="0">
-        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -517,16 +514,16 @@
         <v>11</v>
       </c>
       <c r="C13" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="D13" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s" s="0">
+      <c r="F13" t="s" s="0">
         <v>51</v>
-      </c>
-      <c r="F13" t="s" s="0">
-        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -537,16 +534,16 @@
         <v>11</v>
       </c>
       <c r="C14" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="D14" t="s" s="0">
+      <c r="E14" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="E14" t="s" s="0">
+      <c r="F14" t="s" s="0">
         <v>55</v>
-      </c>
-      <c r="F14" t="s" s="0">
-        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -557,16 +554,16 @@
         <v>11</v>
       </c>
       <c r="C15" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="D15" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="D15" t="s" s="0">
+      <c r="E15" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="E15" t="s" s="0">
+      <c r="F15" t="s" s="0">
         <v>59</v>
-      </c>
-      <c r="F15" t="s" s="0">
-        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -577,16 +574,16 @@
         <v>11</v>
       </c>
       <c r="C16" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="D16" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="E16" t="s" s="0">
+      <c r="F16" t="s" s="0">
         <v>62</v>
-      </c>
-      <c r="F16" t="s" s="0">
-        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -597,16 +594,16 @@
         <v>11</v>
       </c>
       <c r="C17" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="D17" t="s" s="0">
         <v>64</v>
       </c>
-      <c r="D17" t="s" s="0">
+      <c r="E17" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="E17" t="s" s="0">
+      <c r="F17" t="s" s="0">
         <v>66</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
